--- a/data/agriculture/agroclimate-market-registry.xlsx
+++ b/data/agriculture/agroclimate-market-registry.xlsx
@@ -665,15 +665,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -689,20 +690,25 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>district_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>station_id</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>observed_on</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>rainfall_mm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>source_quality</t>
         </is>
@@ -721,16 +727,21 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>D-NORTH</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>WX-NORTH-01</t>
         </is>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="E2" s="1" t="n">
         <v>46113</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>12.5</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
@@ -749,16 +760,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>D-WEST</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>WX-WEST-01</t>
         </is>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="E3" s="1" t="n">
         <v>46113</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>15</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>validated</t>
         </is>
@@ -775,17 +791,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -801,30 +818,35 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>district_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>market_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>commodity</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>price_date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
@@ -843,26 +865,31 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>D-NORTH</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>North Depot Market</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>maize</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="F2" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>0.42</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -881,26 +908,31 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>D-WEST</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>Lowland Market</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>maize</t>
         </is>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="F3" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>0.45</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
@@ -917,17 +949,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -943,30 +976,35 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>district_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>crop</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>planting_window_start</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>planting_window_end</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>harvest_window_start</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>harvest_window_end</t>
         </is>
@@ -985,24 +1023,29 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>D-NORTH</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>maize</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>2026A</t>
         </is>
       </c>
-      <c r="E2" s="1" t="n">
+      <c r="F2" s="1" t="n">
         <v>46082</v>
       </c>
-      <c r="F2" s="1" t="n">
+      <c r="G2" s="1" t="n">
         <v>46142</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="H2" s="1" t="n">
         <v>46235</v>
       </c>
-      <c r="H2" s="1" t="n">
+      <c r="I2" s="1" t="n">
         <v>46295</v>
       </c>
     </row>
@@ -1019,24 +1062,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>D-WEST</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>maize</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>2026A</t>
         </is>
       </c>
-      <c r="E3" s="1" t="n">
+      <c r="F3" s="1" t="n">
         <v>46091</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="G3" s="1" t="n">
         <v>46147</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="H3" s="1" t="n">
         <v>46249</v>
       </c>
-      <c r="H3" s="1" t="n">
+      <c r="I3" s="1" t="n">
         <v>46305</v>
       </c>
     </row>
@@ -1051,17 +1099,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1077,30 +1126,35 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>district_code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>season</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>crop</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>risk_level</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recommended_input_type</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>advisory_text_code</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>active</t>
         </is>
@@ -1119,30 +1173,35 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>D-NORTH</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>2026A</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>maize</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>climate_smart_seed</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>ADV-DRT-SEED</t>
         </is>
       </c>
-      <c r="H2" t="b">
+      <c r="I2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1159,30 +1218,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>D-WEST</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>2026A</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>maize</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>climate_smart_seed</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>ADV-DRT-SEED</t>
         </is>
       </c>
-      <c r="H3" t="b">
+      <c r="I3" t="b">
         <v>1</v>
       </c>
     </row>
